--- a/data/DATOS_MIXTOS.xlsx
+++ b/data/DATOS_MIXTOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\MIXTOS_APP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F9EDC5-7302-48FC-A1A2-8F379524AECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B8F785-211D-46C4-ABC4-4FD5FBCD03A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="352">
   <si>
     <t>NO.</t>
   </si>
@@ -861,12 +861,6 @@
     <t>76.00%</t>
   </si>
   <si>
-    <t>35.00%</t>
-  </si>
-  <si>
-    <t>67.80%</t>
-  </si>
-  <si>
     <t>54.00%</t>
   </si>
   <si>
@@ -987,9 +981,6 @@
     <t>62.00%</t>
   </si>
   <si>
-    <t>59.60%</t>
-  </si>
-  <si>
     <t>63.00%</t>
   </si>
   <si>
@@ -1011,21 +1002,6 @@
     <t>79.60%</t>
   </si>
   <si>
-    <t>41.00%</t>
-  </si>
-  <si>
-    <t>66.60%</t>
-  </si>
-  <si>
-    <t>82.50%</t>
-  </si>
-  <si>
-    <t>38.00%</t>
-  </si>
-  <si>
-    <t>73.60%</t>
-  </si>
-  <si>
     <t>64.75%</t>
   </si>
   <si>
@@ -1087,6 +1063,33 @@
   </si>
   <si>
     <t>75.20%</t>
+  </si>
+  <si>
+    <t>51.50%</t>
+  </si>
+  <si>
+    <t>71.10%</t>
+  </si>
+  <si>
+    <t>58.40%</t>
+  </si>
+  <si>
+    <t>77.00%</t>
+  </si>
+  <si>
+    <t>57.65%</t>
+  </si>
+  <si>
+    <t>73.13%</t>
+  </si>
+  <si>
+    <t>86.50%</t>
+  </si>
+  <si>
+    <t>37.00%</t>
+  </si>
+  <si>
+    <t>76.60%</t>
   </si>
 </sst>
 </file>
@@ -1578,13 +1581,13 @@
         <v>238</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>18</v>
@@ -1631,13 +1634,13 @@
         <v>239</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>270</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>20</v>
@@ -1684,13 +1687,13 @@
         <v>240</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="O4" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="Q4" s="6" t="s">
         <v>20</v>
@@ -1793,13 +1796,13 @@
         <v>274</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>275</v>
+        <v>343</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>276</v>
+        <v>344</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1843,13 +1846,13 @@
         <v>243</v>
       </c>
       <c r="N7" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="P7" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>279</v>
       </c>
       <c r="Q7" s="6" t="s">
         <v>20</v>
@@ -1896,13 +1899,13 @@
         <v>244</v>
       </c>
       <c r="N8" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="P8" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="P8" s="6" t="s">
-        <v>279</v>
       </c>
       <c r="Q8" s="6" t="s">
         <v>20</v>
@@ -1949,13 +1952,13 @@
         <v>245</v>
       </c>
       <c r="N9" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="P9" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="P9" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>20</v>
@@ -2002,13 +2005,13 @@
         <v>246</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>20</v>
@@ -2055,13 +2058,13 @@
         <v>247</v>
       </c>
       <c r="N11" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="P11" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>289</v>
       </c>
       <c r="Q11" s="6" t="s">
         <v>20</v>
@@ -2108,13 +2111,13 @@
         <v>248</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>20</v>
@@ -2161,16 +2164,16 @@
         <v>249</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2214,13 +2217,13 @@
         <v>250</v>
       </c>
       <c r="N14" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="P14" s="6" t="s">
         <v>290</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>292</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>20</v>
@@ -2267,13 +2270,13 @@
         <v>251</v>
       </c>
       <c r="N15" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="P15" s="6" t="s">
         <v>293</v>
-      </c>
-      <c r="O15" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>295</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>20</v>
@@ -2320,13 +2323,13 @@
         <v>252</v>
       </c>
       <c r="N16" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="P16" s="6" t="s">
         <v>296</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>20</v>
@@ -2373,13 +2376,13 @@
         <v>253</v>
       </c>
       <c r="N17" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="P17" s="6" t="s">
         <v>299</v>
-      </c>
-      <c r="O17" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="P17" s="6" t="s">
-        <v>301</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>20</v>
@@ -2426,16 +2429,16 @@
         <v>254</v>
       </c>
       <c r="N18" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="O18" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>304</v>
-      </c>
       <c r="Q18" s="6" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2479,13 +2482,13 @@
         <v>255</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>20</v>
@@ -2532,13 +2535,13 @@
         <v>256</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>20</v>
@@ -2585,13 +2588,13 @@
         <v>257</v>
       </c>
       <c r="N21" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="O21" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="P21" s="6" t="s">
         <v>309</v>
-      </c>
-      <c r="O21" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="P21" s="6" t="s">
-        <v>311</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>20</v>
@@ -2638,13 +2641,13 @@
         <v>258</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="Q22" s="6" t="s">
         <v>20</v>
@@ -2691,13 +2694,13 @@
         <v>259</v>
       </c>
       <c r="N23" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="O23" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="P23" s="6" t="s">
         <v>313</v>
-      </c>
-      <c r="O23" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="P23" s="6" t="s">
-        <v>315</v>
       </c>
       <c r="Q23" s="6" t="s">
         <v>18</v>
@@ -2744,13 +2747,13 @@
         <v>260</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="Q24" s="6" t="s">
         <v>20</v>
@@ -2797,13 +2800,13 @@
         <v>261</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="Q25" s="6" t="s">
         <v>20</v>
@@ -2850,13 +2853,13 @@
         <v>262</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="Q26" s="6" t="s">
         <v>20</v>
@@ -2903,16 +2906,16 @@
         <v>263</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2956,13 +2959,13 @@
         <v>264</v>
       </c>
       <c r="N28" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="O28" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="P28" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>279</v>
       </c>
       <c r="Q28" s="6" t="s">
         <v>20</v>
@@ -3009,16 +3012,16 @@
         <v>265</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>274</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3062,16 +3065,16 @@
         <v>266</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>296</v>
+        <v>346</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>20</v>
+        <v>333</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3115,16 +3118,16 @@
         <v>267</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>341</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3168,13 +3171,13 @@
         <v>172</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="Q32" s="6" t="s">
         <v>20</v>
@@ -3221,13 +3224,13 @@
         <v>268</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="Q33" s="6" t="s">
         <v>20</v>
@@ -3274,13 +3277,13 @@
         <v>172</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>20</v>
@@ -3327,13 +3330,13 @@
         <v>172</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>20</v>
@@ -3380,13 +3383,13 @@
         <v>172</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>20</v>
@@ -3433,13 +3436,13 @@
         <v>172</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>20</v>
@@ -3486,13 +3489,13 @@
         <v>172</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>20</v>
@@ -3539,16 +3542,16 @@
         <v>172</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>269</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
